--- a/HH data.xlsx
+++ b/HH data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mnnso-my.sharepoint.com/personal/undral_nso_mn/Documents/10.Personnal/6.Projects_with_others/FAO_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\PoU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_E1925D0809DA109812A00E8CF22487FB7B1797FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDAFC4F-FEB0-4A28-8AB4-808359A813AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A502085-A5C3-4C2B-884C-9BBADDB2DC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtraInfo" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -37,6 +37,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2222,6 +2225,9 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2230,6 +2236,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2246,16 +2255,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4648,20 +4651,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>583</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12" ht="39" customHeight="1">
       <c r="A2" s="10"/>
@@ -4669,15 +4672,15 @@
       <c r="C2" s="3"/>
       <c r="D2" s="10"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>422</v>
       </c>
-      <c r="G2" s="38"/>
+      <c r="G2" s="39"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="J2" s="38"/>
+      <c r="J2" s="39"/>
       <c r="K2" s="3"/>
       <c r="L2" s="10"/>
     </row>
@@ -18208,20 +18211,20 @@
       <c r="L583" s="3"/>
     </row>
     <row r="584" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A584" s="28" t="s">
+      <c r="A584" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B584" s="29"/>
-      <c r="C584" s="29"/>
-      <c r="D584" s="29"/>
-      <c r="E584" s="29"/>
-      <c r="F584" s="29"/>
-      <c r="G584" s="29"/>
-      <c r="H584" s="29"/>
-      <c r="I584" s="29"/>
-      <c r="J584" s="29"/>
-      <c r="K584" s="29"/>
-      <c r="L584" s="29"/>
+      <c r="B584" s="30"/>
+      <c r="C584" s="30"/>
+      <c r="D584" s="30"/>
+      <c r="E584" s="30"/>
+      <c r="F584" s="30"/>
+      <c r="G584" s="30"/>
+      <c r="H584" s="30"/>
+      <c r="I584" s="30"/>
+      <c r="J584" s="30"/>
+      <c r="K584" s="30"/>
+      <c r="L584" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -18254,15 +18257,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>584</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="90" customHeight="1">
       <c r="A2" s="10"/>
@@ -29274,15 +29277,15 @@
       <c r="G582" s="3"/>
     </row>
     <row r="583" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A583" s="28" t="s">
+      <c r="A583" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B583" s="29"/>
-      <c r="C583" s="29"/>
-      <c r="D583" s="29"/>
-      <c r="E583" s="29"/>
-      <c r="F583" s="29"/>
-      <c r="G583" s="29"/>
+      <c r="B583" s="30"/>
+      <c r="C583" s="30"/>
+      <c r="D583" s="30"/>
+      <c r="E583" s="30"/>
+      <c r="F583" s="30"/>
+      <c r="G583" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -29317,6 +29320,8 @@
     <col min="12" max="12" width="15.140625" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" customWidth="1"/>
     <col min="14" max="14" width="19.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="77.25" customHeight="1">
@@ -29360,10 +29365,10 @@
       <c r="N1" s="23" t="s">
         <v>593</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="28" t="s">
         <v>609</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="28" t="s">
         <v>610</v>
       </c>
     </row>
@@ -29800,14 +29805,14 @@
       <c r="F47" s="3"/>
     </row>
     <row r="48" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -29837,18 +29842,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" ht="51.75" customHeight="1">
       <c r="A2" s="10"/>
@@ -31669,18 +31674,18 @@
       <c r="J132" s="3"/>
     </row>
     <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A133" s="28" t="s">
+      <c r="A133" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B133" s="29"/>
-      <c r="C133" s="29"/>
-      <c r="D133" s="29"/>
-      <c r="E133" s="29"/>
-      <c r="F133" s="29"/>
-      <c r="G133" s="29"/>
-      <c r="H133" s="29"/>
-      <c r="I133" s="29"/>
-      <c r="J133" s="29"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="30"/>
+      <c r="E133" s="30"/>
+      <c r="F133" s="30"/>
+      <c r="G133" s="30"/>
+      <c r="H133" s="30"/>
+      <c r="I133" s="30"/>
+      <c r="J133" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -31722,19 +31727,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="2" spans="1:24" ht="16.5" customHeight="1">
       <c r="A2" s="15"/>
@@ -31742,42 +31747,42 @@
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="34" t="s">
         <v>596</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32" t="s">
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34" t="s">
         <v>597</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="33" t="s">
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="35"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="37"/>
       <c r="X2" s="20" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="70.5" customHeight="1">
       <c r="A3" s="10"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="33" t="s">
         <v>602</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
       <c r="F3" s="10" t="s">
         <v>443</v>
       </c>
@@ -32317,49 +32322,49 @@
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="32" t="s">
         <v>444</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
     </row>
     <row r="24" spans="1:11" ht="39" customHeight="1">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="32" t="s">
         <v>445</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
     </row>
     <row r="25" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>446</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
     </row>
     <row r="26" spans="1:11" ht="13.5" customHeight="1">
       <c r="A26" s="3"/>
@@ -32388,22 +32393,24 @@
       <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:W2"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A24:K24"/>
@@ -32411,8 +32418,6 @@
     <mergeCell ref="A28:K28"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:W2"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <hyperlinks>
@@ -32437,13 +32442,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>594</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" ht="77.25" customHeight="1">
       <c r="A2" s="10"/>
@@ -36669,13 +36674,13 @@
       <c r="E253" s="3"/>
     </row>
     <row r="254" spans="1:5" ht="13.5" customHeight="1">
-      <c r="A254" s="28" t="s">
+      <c r="A254" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B254" s="29"/>
-      <c r="C254" s="29"/>
-      <c r="D254" s="29"/>
-      <c r="E254" s="29"/>
+      <c r="B254" s="30"/>
+      <c r="C254" s="30"/>
+      <c r="D254" s="30"/>
+      <c r="E254" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -36707,26 +36712,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>603</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="47.25" customHeight="1">
       <c r="A2" s="17" t="s">
         <v>600</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>595</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
       <c r="F2" s="18" t="s">
         <v>443</v>
       </c>
@@ -40444,15 +40449,15 @@
       <c r="G251" s="3"/>
     </row>
     <row r="252" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A252" s="28" t="s">
+      <c r="A252" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B252" s="28"/>
-      <c r="C252" s="28"/>
-      <c r="D252" s="28"/>
-      <c r="E252" s="28"/>
-      <c r="F252" s="29"/>
-      <c r="G252" s="29"/>
+      <c r="B252" s="29"/>
+      <c r="C252" s="29"/>
+      <c r="D252" s="29"/>
+      <c r="E252" s="29"/>
+      <c r="F252" s="30"/>
+      <c r="G252" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -40484,14 +40489,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>601</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" ht="77.25" customHeight="1">
       <c r="A2" s="10"/>
@@ -52806,14 +52811,14 @@
       <c r="F625" s="3"/>
     </row>
     <row r="626" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A626" s="28" t="s">
+      <c r="A626" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B626" s="29"/>
-      <c r="C626" s="29"/>
-      <c r="D626" s="29"/>
-      <c r="E626" s="29"/>
-      <c r="F626" s="29"/>
+      <c r="B626" s="30"/>
+      <c r="C626" s="30"/>
+      <c r="D626" s="30"/>
+      <c r="E626" s="30"/>
+      <c r="F626" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -52845,34 +52850,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>579</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="39" t="s">
         <v>448</v>
       </c>
-      <c r="C2" s="38"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="I2" s="38"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="77.25" customHeight="1">
       <c r="A3" s="10"/>
@@ -53950,17 +53955,17 @@
       <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -53995,34 +54000,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>580</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="39" t="s">
         <v>448</v>
       </c>
-      <c r="C2" s="38"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="I2" s="38"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="77.25" customHeight="1">
       <c r="A3" s="10"/>
@@ -56620,17 +56625,17 @@
       <c r="I117" s="3"/>
     </row>
     <row r="118" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A118" s="28" t="s">
+      <c r="A118" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="B118" s="29"/>
-      <c r="C118" s="29"/>
-      <c r="D118" s="29"/>
-      <c r="E118" s="29"/>
-      <c r="F118" s="29"/>
-      <c r="G118" s="29"/>
-      <c r="H118" s="29"/>
-      <c r="I118" s="29"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="30"/>
+      <c r="H118" s="30"/>
+      <c r="I118" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="5">
